--- a/Aug 2026.xlsx
+++ b/Aug 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abutalib/Projects/personal-accounting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAA0E61-3367-7F4D-AA90-1084EB42AC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEB51A4-529B-5041-97B4-32F2AFF05FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29840" windowHeight="17380" xr2:uid="{7E62CB60-3E82-0E48-87C0-051D0E492E72}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="167">
   <si>
     <t>فاتورة الكهرباء</t>
   </si>
@@ -535,6 +535,9 @@
   </si>
   <si>
     <t>ملابس منى (ممكن ترجع)</t>
+  </si>
+  <si>
+    <t>زيت السيارة</t>
   </si>
 </sst>
 </file>
@@ -675,13 +678,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1084,14 +1087,14 @@
       <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20" t="s">
+      <c r="F1" s="21"/>
+      <c r="G1" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1" s="21"/>
       <c r="I1" s="4"/>
       <c r="J1" s="3" t="s">
         <v>17</v>
@@ -1152,7 +1155,7 @@
       </c>
       <c r="W2" s="3">
         <f>SUM(W7:W16)</f>
-        <v>11996</v>
+        <v>18311</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="3" t="s">
@@ -1160,7 +1163,7 @@
       </c>
       <c r="AA2" s="3">
         <f>SUM(AA7:AA35)</f>
-        <v>24996</v>
+        <v>31311</v>
       </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="3" t="s">
@@ -1168,7 +1171,7 @@
       </c>
       <c r="AD2" s="3">
         <f>SUM(AD7:AD21)</f>
-        <v>3044</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
@@ -1194,7 +1197,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(H7:H29)</f>
-        <v>2000</v>
+        <v>2150</v>
       </c>
       <c r="I3" s="4"/>
       <c r="R3" s="4"/>
@@ -1210,7 +1213,7 @@
       </c>
       <c r="AD3" s="3">
         <f>AA21-AD2</f>
-        <v>-1037</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
@@ -1260,7 +1263,7 @@
       </c>
       <c r="H5" s="3">
         <f>H4-H3</f>
-        <v>3565</v>
+        <v>3415</v>
       </c>
       <c r="I5" s="4"/>
       <c r="R5" s="4"/>
@@ -1287,10 +1290,10 @@
       <c r="O6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="P6" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="Q6" s="19"/>
+      <c r="Q6" s="20"/>
       <c r="R6" s="9"/>
       <c r="U6" s="9"/>
       <c r="X6" s="9"/>
@@ -1408,9 +1411,7 @@
       <c r="AC8" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AD8" s="15">
-        <v>957</v>
-      </c>
+      <c r="AD8" s="15"/>
       <c r="AE8" s="3" t="s">
         <v>84</v>
       </c>
@@ -1447,7 +1448,7 @@
       </c>
       <c r="W9" s="3">
         <f>H5</f>
-        <v>3565</v>
+        <v>3415</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="3" t="s">
@@ -1524,7 +1525,7 @@
       <c r="D11" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="19">
         <v>1898</v>
       </c>
       <c r="I11" s="4"/>
@@ -1545,7 +1546,7 @@
       </c>
       <c r="W11" s="3">
         <f>J32</f>
-        <v>5381</v>
+        <v>11846</v>
       </c>
       <c r="X11" s="4"/>
       <c r="Y11" s="1" t="s">
@@ -1863,6 +1864,12 @@
     </row>
     <row r="21" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C21" s="4"/>
+      <c r="D21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="3">
+        <v>150</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="3" t="s">
         <v>15</v>
@@ -2060,7 +2067,7 @@
       </c>
       <c r="AA31" s="3">
         <f>W2</f>
-        <v>11996</v>
+        <v>18311</v>
       </c>
       <c r="AB31" s="3"/>
     </row>
@@ -2076,7 +2083,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3">
         <f>الأرصدة!M29-'مصاريف الشهر'!D32</f>
-        <v>5381</v>
+        <v>11846</v>
       </c>
       <c r="O32" s="3">
         <f>E3</f>
@@ -2088,7 +2095,7 @@
       </c>
       <c r="Q32" s="3">
         <f>J32-SUM(O32:P32)</f>
-        <v>0</v>
+        <v>6465</v>
       </c>
       <c r="R32" s="3"/>
       <c r="U32" s="3"/>
@@ -2098,7 +2105,7 @@
     <row r="33" spans="3:28" x14ac:dyDescent="0.3">
       <c r="J33" s="3">
         <f>J32-F15</f>
-        <v>5381</v>
+        <v>11846</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>95</v>
@@ -2336,7 +2343,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="11">
         <f>SUM(D6:D20)</f>
-        <v>5150</v>
+        <v>8200</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
@@ -2357,7 +2364,7 @@
       <c r="N2" s="4"/>
       <c r="O2" s="11">
         <f>SUM(Q6:Q20)</f>
-        <v>74094</v>
+        <v>77509</v>
       </c>
       <c r="P2" s="11"/>
       <c r="R2" s="4"/>
@@ -3132,9 +3139,15 @@
       <c r="L15" s="3"/>
       <c r="M15" s="11"/>
       <c r="N15" s="4"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="11"/>
+      <c r="O15" s="3">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>3415</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="3">
         <v>3</v>
@@ -3170,7 +3183,9 @@
       <c r="C16" s="3">
         <v>8</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="11">
+        <v>3050</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="3">
         <v>10</v>
@@ -3496,7 +3511,7 @@
       </c>
       <c r="M23" s="6">
         <f>O2-S2</f>
-        <v>20334</v>
+        <v>23749</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="3"/>
@@ -3528,7 +3543,7 @@
       </c>
       <c r="M24" s="6">
         <f>C2</f>
-        <v>5150</v>
+        <v>8200</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="3"/>
@@ -3668,7 +3683,7 @@
       </c>
       <c r="Y27" s="12">
         <f>M29-W27</f>
-        <v>-23574</v>
+        <v>-17109</v>
       </c>
       <c r="AE27">
         <f>SUM(AE24:AE26)</f>
@@ -3716,7 +3731,7 @@
       </c>
       <c r="M29" s="6">
         <f>SUM(M23:M28)</f>
-        <v>11692</v>
+        <v>18157</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="3"/>
@@ -3740,7 +3755,7 @@
       </c>
       <c r="M30" s="6">
         <f>M23+M27+M26</f>
-        <v>3534</v>
+        <v>6949</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
